--- a/Asistencias/Copia de Tareitas.xlsx
+++ b/Asistencias/Copia de Tareitas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/carlosmartinez/Proyectos/Github/CalculoDiferencialTNM/Asistencias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8310AEE-1F8F-0A46-9E98-D3F49A4BCAE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C6FF9D-256F-E646-B458-89851ECF8D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="5A_CD" sheetId="4" r:id="rId1"/>
@@ -2897,7 +2897,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3076,6 +3076,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -3142,12 +3145,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="27" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3157,9 +3154,17 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3529,11 +3534,11 @@
       <c r="C1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="M1" s="95" t="s">
+      <c r="M1" s="96" t="s">
         <v>752</v>
       </c>
-      <c r="N1" s="96"/>
-      <c r="O1" s="96"/>
+      <c r="N1" s="97"/>
+      <c r="O1" s="97"/>
       <c r="P1" s="36"/>
       <c r="Q1" s="36"/>
       <c r="R1" s="29"/>
@@ -3558,7 +3563,7 @@
       <c r="BF1" s="25"/>
       <c r="BG1" s="25"/>
       <c r="BH1" s="9"/>
-      <c r="BI1" s="90" t="s">
+      <c r="BI1" s="91" t="s">
         <v>770</v>
       </c>
       <c r="BM1" s="25"/>
@@ -3579,107 +3584,107 @@
       <c r="H2" s="18"/>
       <c r="I2" s="9"/>
       <c r="J2" s="52"/>
-      <c r="K2" s="88" t="s">
+      <c r="K2" s="89" t="s">
         <v>759</v>
       </c>
       <c r="L2" s="36"/>
-      <c r="M2" s="97" t="s">
+      <c r="M2" s="98" t="s">
         <v>760</v>
       </c>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="98"/>
-      <c r="Q2" s="98"/>
-      <c r="R2" s="99"/>
-      <c r="S2" s="100" t="s">
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="P2" s="99"/>
+      <c r="Q2" s="99"/>
+      <c r="R2" s="100"/>
+      <c r="S2" s="101" t="s">
         <v>761</v>
       </c>
-      <c r="T2" s="98"/>
-      <c r="U2" s="98"/>
-      <c r="V2" s="98"/>
-      <c r="W2" s="98"/>
-      <c r="X2" s="101"/>
-      <c r="Y2" s="97" t="s">
+      <c r="T2" s="99"/>
+      <c r="U2" s="99"/>
+      <c r="V2" s="99"/>
+      <c r="W2" s="99"/>
+      <c r="X2" s="102"/>
+      <c r="Y2" s="98" t="s">
         <v>762</v>
       </c>
-      <c r="Z2" s="98"/>
-      <c r="AA2" s="98"/>
-      <c r="AB2" s="98"/>
-      <c r="AC2" s="98"/>
-      <c r="AD2" s="98"/>
-      <c r="AE2" s="100" t="s">
+      <c r="Z2" s="99"/>
+      <c r="AA2" s="99"/>
+      <c r="AB2" s="99"/>
+      <c r="AC2" s="99"/>
+      <c r="AD2" s="99"/>
+      <c r="AE2" s="101" t="s">
         <v>763</v>
       </c>
-      <c r="AF2" s="98"/>
-      <c r="AG2" s="98"/>
-      <c r="AH2" s="98"/>
-      <c r="AI2" s="98"/>
-      <c r="AJ2" s="101"/>
-      <c r="AK2" s="87" t="s">
+      <c r="AF2" s="99"/>
+      <c r="AG2" s="99"/>
+      <c r="AH2" s="99"/>
+      <c r="AI2" s="99"/>
+      <c r="AJ2" s="102"/>
+      <c r="AK2" s="88" t="s">
         <v>766</v>
       </c>
-      <c r="AL2" s="87"/>
-      <c r="AM2" s="87"/>
-      <c r="AN2" s="87"/>
-      <c r="AO2" s="87"/>
-      <c r="AP2" s="87"/>
-      <c r="AQ2" s="86" t="s">
+      <c r="AL2" s="88"/>
+      <c r="AM2" s="88"/>
+      <c r="AN2" s="88"/>
+      <c r="AO2" s="88"/>
+      <c r="AP2" s="88"/>
+      <c r="AQ2" s="87" t="s">
         <v>767</v>
       </c>
-      <c r="AR2" s="87"/>
-      <c r="AS2" s="87"/>
-      <c r="AT2" s="87"/>
-      <c r="AU2" s="87"/>
-      <c r="AV2" s="87"/>
-      <c r="AW2" s="86" t="s">
+      <c r="AR2" s="88"/>
+      <c r="AS2" s="88"/>
+      <c r="AT2" s="88"/>
+      <c r="AU2" s="88"/>
+      <c r="AV2" s="88"/>
+      <c r="AW2" s="87" t="s">
         <v>768</v>
       </c>
-      <c r="AX2" s="87"/>
-      <c r="AY2" s="87"/>
-      <c r="AZ2" s="87"/>
-      <c r="BA2" s="87"/>
-      <c r="BB2" s="87"/>
-      <c r="BC2" s="86" t="s">
+      <c r="AX2" s="88"/>
+      <c r="AY2" s="88"/>
+      <c r="AZ2" s="88"/>
+      <c r="BA2" s="88"/>
+      <c r="BB2" s="88"/>
+      <c r="BC2" s="87" t="s">
         <v>769</v>
       </c>
-      <c r="BD2" s="87"/>
-      <c r="BE2" s="87"/>
-      <c r="BF2" s="87"/>
-      <c r="BG2" s="87"/>
-      <c r="BH2" s="87"/>
-      <c r="BI2" s="90"/>
-      <c r="BJ2" s="86" t="s">
+      <c r="BD2" s="88"/>
+      <c r="BE2" s="88"/>
+      <c r="BF2" s="88"/>
+      <c r="BG2" s="88"/>
+      <c r="BH2" s="88"/>
+      <c r="BI2" s="91"/>
+      <c r="BJ2" s="87" t="s">
         <v>757</v>
       </c>
-      <c r="BK2" s="87"/>
-      <c r="BL2" s="87"/>
-      <c r="BM2" s="87"/>
-      <c r="BN2" s="87"/>
-      <c r="BO2" s="87"/>
-      <c r="BP2" s="86" t="s">
+      <c r="BK2" s="88"/>
+      <c r="BL2" s="88"/>
+      <c r="BM2" s="88"/>
+      <c r="BN2" s="88"/>
+      <c r="BO2" s="88"/>
+      <c r="BP2" s="87" t="s">
         <v>757</v>
       </c>
-      <c r="BQ2" s="87"/>
-      <c r="BR2" s="87"/>
-      <c r="BS2" s="87"/>
-      <c r="BT2" s="87"/>
-      <c r="BU2" s="87"/>
-      <c r="BV2" s="86" t="s">
+      <c r="BQ2" s="88"/>
+      <c r="BR2" s="88"/>
+      <c r="BS2" s="88"/>
+      <c r="BT2" s="88"/>
+      <c r="BU2" s="88"/>
+      <c r="BV2" s="87" t="s">
         <v>757</v>
       </c>
-      <c r="BW2" s="87"/>
-      <c r="BX2" s="87"/>
-      <c r="BY2" s="87"/>
-      <c r="BZ2" s="87"/>
-      <c r="CA2" s="87"/>
-      <c r="CB2" s="86" t="s">
+      <c r="BW2" s="88"/>
+      <c r="BX2" s="88"/>
+      <c r="BY2" s="88"/>
+      <c r="BZ2" s="88"/>
+      <c r="CA2" s="88"/>
+      <c r="CB2" s="87" t="s">
         <v>757</v>
       </c>
-      <c r="CC2" s="87"/>
-      <c r="CD2" s="87"/>
-      <c r="CE2" s="87"/>
-      <c r="CF2" s="87"/>
-      <c r="CG2" s="87"/>
+      <c r="CC2" s="88"/>
+      <c r="CD2" s="88"/>
+      <c r="CE2" s="88"/>
+      <c r="CF2" s="88"/>
+      <c r="CG2" s="88"/>
     </row>
     <row r="3" spans="1:85" ht="48" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
@@ -3712,7 +3717,7 @@
       <c r="J3" s="24" t="s">
         <v>771</v>
       </c>
-      <c r="K3" s="89"/>
+      <c r="K3" s="90"/>
       <c r="L3" s="56" t="s">
         <v>773</v>
       </c>
@@ -3860,7 +3865,7 @@
       <c r="BH3" s="9" t="s">
         <v>756</v>
       </c>
-      <c r="BI3" s="91"/>
+      <c r="BI3" s="92"/>
       <c r="BJ3" s="18" t="s">
         <v>753</v>
       </c>
@@ -4122,7 +4127,7 @@
         <f>AVERAGE(BC4:BG4)</f>
         <v>0</v>
       </c>
-      <c r="BI4" s="92"/>
+      <c r="BI4" s="93"/>
       <c r="BJ4" s="5"/>
       <c r="BK4" s="5"/>
       <c r="BL4" s="5"/>
@@ -4346,7 +4351,7 @@
         <f t="shared" ref="BH5:BH40" si="10">AVERAGE(BC5:BG5)</f>
         <v>0</v>
       </c>
-      <c r="BI5" s="93"/>
+      <c r="BI5" s="94"/>
       <c r="BJ5" s="7"/>
       <c r="BK5" s="7"/>
       <c r="BL5" s="7"/>
@@ -4570,7 +4575,7 @@
         <f t="shared" si="10"/>
         <v>0.5</v>
       </c>
-      <c r="BI6" s="93"/>
+      <c r="BI6" s="94"/>
       <c r="BJ6" s="5"/>
       <c r="BK6" s="5"/>
       <c r="BL6" s="5"/>
@@ -4792,7 +4797,7 @@
         <f t="shared" si="10"/>
         <v>0.05</v>
       </c>
-      <c r="BI7" s="93"/>
+      <c r="BI7" s="94"/>
       <c r="BJ7" s="7"/>
       <c r="BK7" s="7"/>
       <c r="BL7" s="7"/>
@@ -5014,7 +5019,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BI8" s="93"/>
+      <c r="BI8" s="94"/>
       <c r="BJ8" s="5"/>
       <c r="BK8" s="5"/>
       <c r="BL8" s="5"/>
@@ -5156,7 +5161,7 @@
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BI9" s="93"/>
+      <c r="BI9" s="94"/>
       <c r="BJ9" s="61"/>
       <c r="BK9" s="61"/>
       <c r="BL9" s="61"/>
@@ -5294,7 +5299,7 @@
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BI10" s="93"/>
+      <c r="BI10" s="94"/>
       <c r="BJ10" s="61"/>
       <c r="BK10" s="61"/>
       <c r="BL10" s="61"/>
@@ -5520,7 +5525,7 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="BI11" s="93"/>
+      <c r="BI11" s="94"/>
       <c r="BJ11" s="7"/>
       <c r="BK11" s="7"/>
       <c r="BL11" s="7"/>
@@ -5744,7 +5749,7 @@
         <f t="shared" si="10"/>
         <v>0.4</v>
       </c>
-      <c r="BI12" s="93"/>
+      <c r="BI12" s="94"/>
       <c r="BJ12" s="5"/>
       <c r="BK12" s="5"/>
       <c r="BL12" s="5"/>
@@ -5966,7 +5971,7 @@
         <f t="shared" si="10"/>
         <v>0.6</v>
       </c>
-      <c r="BI13" s="93"/>
+      <c r="BI13" s="94"/>
       <c r="BJ13" s="7"/>
       <c r="BK13" s="7"/>
       <c r="BL13" s="7"/>
@@ -6188,7 +6193,7 @@
         <f t="shared" si="10"/>
         <v>0.48</v>
       </c>
-      <c r="BI14" s="93"/>
+      <c r="BI14" s="94"/>
       <c r="BJ14" s="5"/>
       <c r="BK14" s="5"/>
       <c r="BL14" s="5"/>
@@ -6406,7 +6411,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BI15" s="93"/>
+      <c r="BI15" s="94"/>
       <c r="BJ15" s="7"/>
       <c r="BK15" s="7"/>
       <c r="BL15" s="7"/>
@@ -6628,7 +6633,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BI16" s="93"/>
+      <c r="BI16" s="94"/>
       <c r="BJ16" s="5"/>
       <c r="BK16" s="5"/>
       <c r="BL16" s="5"/>
@@ -6852,7 +6857,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BI17" s="93"/>
+      <c r="BI17" s="94"/>
       <c r="BJ17" s="7">
         <v>0.75</v>
       </c>
@@ -7002,7 +7007,7 @@
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BI18" s="93"/>
+      <c r="BI18" s="94"/>
       <c r="BJ18" s="61"/>
       <c r="BK18" s="61"/>
       <c r="BL18" s="61"/>
@@ -7226,7 +7231,7 @@
         <f t="shared" si="10"/>
         <v>0.2</v>
       </c>
-      <c r="BI19" s="93"/>
+      <c r="BI19" s="94"/>
       <c r="BJ19" s="7">
         <v>1</v>
       </c>
@@ -7468,7 +7473,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BI20" s="93"/>
+      <c r="BI20" s="94"/>
       <c r="BJ20" s="5"/>
       <c r="BK20" s="5"/>
       <c r="BL20" s="5"/>
@@ -7608,7 +7613,7 @@
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BI21" s="93"/>
+      <c r="BI21" s="94"/>
       <c r="BJ21" s="61"/>
       <c r="BK21" s="61"/>
       <c r="BL21" s="61"/>
@@ -7828,7 +7833,7 @@
         <f t="shared" si="10"/>
         <v>0.25</v>
       </c>
-      <c r="BI22" s="93"/>
+      <c r="BI22" s="94"/>
       <c r="BJ22" s="5"/>
       <c r="BK22" s="5"/>
       <c r="BL22" s="5"/>
@@ -7966,7 +7971,7 @@
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BI23" s="93"/>
+      <c r="BI23" s="94"/>
       <c r="BJ23" s="61"/>
       <c r="BK23" s="61"/>
       <c r="BL23" s="61"/>
@@ -8106,7 +8111,7 @@
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BI24" s="93"/>
+      <c r="BI24" s="94"/>
       <c r="BJ24" s="61"/>
       <c r="BK24" s="61"/>
       <c r="BL24" s="61"/>
@@ -8244,7 +8249,7 @@
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BI25" s="93"/>
+      <c r="BI25" s="94"/>
       <c r="BJ25" s="61"/>
       <c r="BK25" s="61"/>
       <c r="BL25" s="61"/>
@@ -8466,7 +8471,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BI26" s="93"/>
+      <c r="BI26" s="94"/>
       <c r="BJ26" s="5"/>
       <c r="BK26" s="5"/>
       <c r="BL26" s="5"/>
@@ -8688,7 +8693,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BI27" s="93"/>
+      <c r="BI27" s="94"/>
       <c r="BJ27" s="7"/>
       <c r="BK27" s="7"/>
       <c r="BL27" s="7"/>
@@ -8912,7 +8917,7 @@
         <f t="shared" si="10"/>
         <v>0.3</v>
       </c>
-      <c r="BI28" s="93"/>
+      <c r="BI28" s="94"/>
       <c r="BJ28" s="5"/>
       <c r="BK28" s="5"/>
       <c r="BL28" s="5"/>
@@ -9134,7 +9139,7 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="BI29" s="93"/>
+      <c r="BI29" s="94"/>
       <c r="BJ29" s="7"/>
       <c r="BK29" s="7"/>
       <c r="BL29" s="7"/>
@@ -9356,7 +9361,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BI30" s="93"/>
+      <c r="BI30" s="94"/>
       <c r="BJ30" s="5"/>
       <c r="BK30" s="5"/>
       <c r="BL30" s="5"/>
@@ -9578,7 +9583,7 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="BI31" s="93"/>
+      <c r="BI31" s="94"/>
       <c r="BJ31" s="7"/>
       <c r="BK31" s="7"/>
       <c r="BL31" s="7"/>
@@ -9808,7 +9813,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BI32" s="93"/>
+      <c r="BI32" s="94"/>
       <c r="BJ32" s="5"/>
       <c r="BK32" s="5"/>
       <c r="BL32" s="5"/>
@@ -10028,7 +10033,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BI33" s="93"/>
+      <c r="BI33" s="94"/>
       <c r="BJ33" s="7"/>
       <c r="BK33" s="7"/>
       <c r="BL33" s="7"/>
@@ -10250,7 +10255,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BI34" s="93"/>
+      <c r="BI34" s="94"/>
       <c r="BJ34" s="5"/>
       <c r="BK34" s="5"/>
       <c r="BL34" s="5"/>
@@ -10474,7 +10479,7 @@
         <f t="shared" si="10"/>
         <v>0.2</v>
       </c>
-      <c r="BI35" s="93"/>
+      <c r="BI35" s="94"/>
       <c r="BJ35" s="7"/>
       <c r="BK35" s="7"/>
       <c r="BL35" s="7"/>
@@ -10696,7 +10701,7 @@
         <f t="shared" si="10"/>
         <v>0.6</v>
       </c>
-      <c r="BI36" s="93"/>
+      <c r="BI36" s="94"/>
       <c r="BJ36" s="5">
         <v>0.5</v>
       </c>
@@ -10926,7 +10931,7 @@
         <f t="shared" si="10"/>
         <v>0.05</v>
       </c>
-      <c r="BI37" s="93"/>
+      <c r="BI37" s="94"/>
       <c r="BJ37" s="7"/>
       <c r="BK37" s="7"/>
       <c r="BL37" s="7"/>
@@ -11150,7 +11155,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BI38" s="93"/>
+      <c r="BI38" s="94"/>
       <c r="BJ38" s="5"/>
       <c r="BK38" s="5"/>
       <c r="BL38" s="5"/>
@@ -11372,7 +11377,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BI39" s="93"/>
+      <c r="BI39" s="94"/>
       <c r="BJ39" s="7"/>
       <c r="BK39" s="7"/>
       <c r="BL39" s="7"/>
@@ -11594,7 +11599,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BI40" s="94"/>
+      <c r="BI40" s="95"/>
       <c r="BJ40" s="5"/>
       <c r="BK40" s="5"/>
       <c r="BL40" s="5"/>
@@ -12343,59 +12348,61 @@
       <c r="AM10" s="61"/>
       <c r="AN10" s="61"/>
     </row>
-    <row r="11" spans="1:40" s="70" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="61" t="s">
+    <row r="11" spans="1:40" s="116" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="114" t="s">
         <v>205</v>
       </c>
-      <c r="B11" s="61">
-        <v>1</v>
-      </c>
-      <c r="C11" s="62" t="s">
+      <c r="B11" s="114">
+        <v>1</v>
+      </c>
+      <c r="C11" s="115" t="s">
         <v>204</v>
       </c>
-      <c r="D11" s="61" t="s">
+      <c r="D11" s="114" t="s">
         <v>168</v>
       </c>
-      <c r="E11" s="61">
-        <v>1</v>
-      </c>
-      <c r="F11" s="61">
-        <v>1</v>
-      </c>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61"/>
-      <c r="J11" s="61"/>
-      <c r="K11" s="61"/>
-      <c r="L11" s="61"/>
-      <c r="M11" s="61"/>
-      <c r="N11" s="61"/>
-      <c r="O11" s="61"/>
-      <c r="P11" s="61"/>
-      <c r="Q11" s="61"/>
-      <c r="R11" s="61"/>
-      <c r="S11" s="61"/>
-      <c r="T11" s="61"/>
-      <c r="U11" s="61"/>
-      <c r="V11" s="61"/>
-      <c r="W11" s="61"/>
-      <c r="X11" s="61"/>
-      <c r="Y11" s="61"/>
-      <c r="Z11" s="61"/>
-      <c r="AA11" s="61"/>
-      <c r="AB11" s="61"/>
-      <c r="AC11" s="61"/>
-      <c r="AD11" s="61"/>
-      <c r="AE11" s="61"/>
-      <c r="AF11" s="61"/>
-      <c r="AG11" s="61"/>
-      <c r="AH11" s="61"/>
-      <c r="AI11" s="61"/>
-      <c r="AJ11" s="61"/>
-      <c r="AK11" s="61"/>
-      <c r="AL11" s="61"/>
-      <c r="AM11" s="61"/>
-      <c r="AN11" s="61"/>
+      <c r="E11" s="114">
+        <v>1</v>
+      </c>
+      <c r="F11" s="114">
+        <v>1</v>
+      </c>
+      <c r="G11" s="114">
+        <v>100</v>
+      </c>
+      <c r="H11" s="114"/>
+      <c r="I11" s="114"/>
+      <c r="J11" s="114"/>
+      <c r="K11" s="114"/>
+      <c r="L11" s="114"/>
+      <c r="M11" s="114"/>
+      <c r="N11" s="114"/>
+      <c r="O11" s="114"/>
+      <c r="P11" s="114"/>
+      <c r="Q11" s="114"/>
+      <c r="R11" s="114"/>
+      <c r="S11" s="114"/>
+      <c r="T11" s="114"/>
+      <c r="U11" s="114"/>
+      <c r="V11" s="114"/>
+      <c r="W11" s="114"/>
+      <c r="X11" s="114"/>
+      <c r="Y11" s="114"/>
+      <c r="Z11" s="114"/>
+      <c r="AA11" s="114"/>
+      <c r="AB11" s="114"/>
+      <c r="AC11" s="114"/>
+      <c r="AD11" s="114"/>
+      <c r="AE11" s="114"/>
+      <c r="AF11" s="114"/>
+      <c r="AG11" s="114"/>
+      <c r="AH11" s="114"/>
+      <c r="AI11" s="114"/>
+      <c r="AJ11" s="114"/>
+      <c r="AK11" s="114"/>
+      <c r="AL11" s="114"/>
+      <c r="AM11" s="114"/>
+      <c r="AN11" s="114"/>
     </row>
     <row r="12" spans="1:40" s="70" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="61" t="s">
@@ -13819,7 +13826,7 @@
       <c r="C2" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="D2" s="113"/>
+      <c r="D2" s="86"/>
       <c r="E2" s="5"/>
       <c r="F2" s="10"/>
       <c r="G2" s="5"/>
@@ -13863,7 +13870,7 @@
       <c r="C3" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="D3" s="113"/>
+      <c r="D3" s="86"/>
       <c r="E3" s="7"/>
       <c r="F3" s="11"/>
       <c r="G3" s="7"/>
@@ -13907,7 +13914,7 @@
       <c r="C4" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="D4" s="113"/>
+      <c r="D4" s="86"/>
       <c r="E4" s="5"/>
       <c r="F4" s="10"/>
       <c r="G4" s="5"/>
@@ -13951,7 +13958,7 @@
       <c r="C5" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="D5" s="113">
+      <c r="D5" s="86">
         <v>70</v>
       </c>
       <c r="E5" s="7"/>
@@ -13997,7 +14004,7 @@
       <c r="C6" s="5" t="s">
         <v>624</v>
       </c>
-      <c r="D6" s="113"/>
+      <c r="D6" s="86"/>
       <c r="E6" s="5"/>
       <c r="F6" s="10"/>
       <c r="G6" s="5"/>
@@ -14041,7 +14048,7 @@
       <c r="C7" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="D7" s="113"/>
+      <c r="D7" s="86"/>
       <c r="E7" s="7"/>
       <c r="F7" s="11"/>
       <c r="G7" s="7"/>
@@ -14085,7 +14092,7 @@
       <c r="C8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="113"/>
+      <c r="D8" s="86"/>
       <c r="E8" s="5"/>
       <c r="F8" s="10"/>
       <c r="G8" s="5"/>
@@ -14129,7 +14136,7 @@
       <c r="C9" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="D9" s="113"/>
+      <c r="D9" s="86"/>
       <c r="E9" s="7"/>
       <c r="F9" s="11"/>
       <c r="G9" s="7"/>
@@ -14173,7 +14180,7 @@
       <c r="C10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="113">
+      <c r="D10" s="86">
         <v>83.75</v>
       </c>
       <c r="E10" s="5"/>
@@ -14219,7 +14226,7 @@
       <c r="C11" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="D11" s="113"/>
+      <c r="D11" s="86"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -14263,7 +14270,7 @@
       <c r="C12" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D12" s="113"/>
+      <c r="D12" s="86"/>
       <c r="E12" s="5"/>
       <c r="F12" s="10"/>
       <c r="G12" s="5"/>
@@ -14307,7 +14314,7 @@
       <c r="C13" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="113">
+      <c r="D13" s="86">
         <v>100</v>
       </c>
       <c r="E13" s="7"/>
@@ -14353,7 +14360,7 @@
       <c r="C14" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="113"/>
+      <c r="D14" s="86"/>
       <c r="E14" s="5"/>
       <c r="F14" s="10"/>
       <c r="G14" s="5"/>
@@ -14397,7 +14404,7 @@
       <c r="C15" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="113"/>
+      <c r="D15" s="86"/>
       <c r="E15" s="7"/>
       <c r="F15" s="11"/>
       <c r="G15" s="7"/>
@@ -14441,7 +14448,7 @@
       <c r="C16" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="D16" s="113"/>
+      <c r="D16" s="86"/>
       <c r="E16" s="5"/>
       <c r="F16" s="10"/>
       <c r="G16" s="5"/>
@@ -14485,7 +14492,7 @@
       <c r="C17" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="D17" s="113"/>
+      <c r="D17" s="86"/>
       <c r="E17" s="7"/>
       <c r="F17" s="11"/>
       <c r="G17" s="7"/>
@@ -14529,7 +14536,7 @@
       <c r="C18" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="D18" s="113">
+      <c r="D18" s="86">
         <v>55</v>
       </c>
       <c r="E18" s="5"/>
@@ -14575,7 +14582,7 @@
       <c r="C19" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="D19" s="113"/>
+      <c r="D19" s="86"/>
       <c r="E19" s="7"/>
       <c r="F19" s="11"/>
       <c r="G19" s="7"/>
@@ -14619,7 +14626,7 @@
       <c r="C20" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="D20" s="113"/>
+      <c r="D20" s="86"/>
       <c r="E20" s="5"/>
       <c r="F20" s="10"/>
       <c r="G20" s="5"/>
@@ -14663,7 +14670,7 @@
       <c r="C21" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="D21" s="113"/>
+      <c r="D21" s="86"/>
       <c r="E21" s="7"/>
       <c r="F21" s="11"/>
       <c r="G21" s="7"/>
@@ -14707,7 +14714,7 @@
       <c r="C22" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="D22" s="113">
+      <c r="D22" s="86">
         <v>15</v>
       </c>
       <c r="E22" s="5"/>
@@ -14753,7 +14760,7 @@
       <c r="C23" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="113"/>
+      <c r="D23" s="86"/>
       <c r="E23" s="7"/>
       <c r="F23" s="11"/>
       <c r="G23" s="7"/>
@@ -14797,7 +14804,7 @@
       <c r="C24" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D24" s="113"/>
+      <c r="D24" s="86"/>
       <c r="E24" s="5"/>
       <c r="F24" s="10"/>
       <c r="G24" s="5"/>
@@ -14841,7 +14848,7 @@
       <c r="C25" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="D25" s="113"/>
+      <c r="D25" s="86"/>
       <c r="E25" s="7"/>
       <c r="F25" s="11"/>
       <c r="G25" s="7"/>
@@ -14885,7 +14892,7 @@
       <c r="C26" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="D26" s="113"/>
+      <c r="D26" s="86"/>
       <c r="E26" s="5"/>
       <c r="F26" s="10"/>
       <c r="G26" s="5"/>
@@ -14929,7 +14936,7 @@
       <c r="C27" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="D27" s="113"/>
+      <c r="D27" s="86"/>
       <c r="E27" s="7"/>
       <c r="F27" s="11"/>
       <c r="G27" s="7"/>
@@ -14973,7 +14980,7 @@
       <c r="C28" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D28" s="113"/>
+      <c r="D28" s="86"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
@@ -15017,7 +15024,7 @@
       <c r="C29" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="D29" s="113"/>
+      <c r="D29" s="86"/>
       <c r="E29" s="7"/>
       <c r="F29" s="11"/>
       <c r="G29" s="7"/>
@@ -15061,7 +15068,7 @@
       <c r="C30" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="D30" s="113"/>
+      <c r="D30" s="86"/>
       <c r="E30" s="5"/>
       <c r="F30" s="10"/>
       <c r="G30" s="5"/>
@@ -15105,7 +15112,7 @@
       <c r="C31" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="D31" s="113"/>
+      <c r="D31" s="86"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="G31" s="7"/>
@@ -15149,7 +15156,7 @@
       <c r="C32" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="D32" s="113"/>
+      <c r="D32" s="86"/>
       <c r="E32" s="5"/>
       <c r="F32" s="10"/>
       <c r="G32" s="5"/>
@@ -15193,7 +15200,7 @@
       <c r="C33" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D33" s="113"/>
+      <c r="D33" s="86"/>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
@@ -15237,7 +15244,7 @@
       <c r="C34" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="D34" s="113"/>
+      <c r="D34" s="86"/>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
@@ -15281,7 +15288,7 @@
       <c r="C35" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D35" s="113">
+      <c r="D35" s="86">
         <v>0</v>
       </c>
       <c r="E35" s="7"/>
@@ -17189,8 +17196,8 @@
       <c r="F3" s="5" t="s">
         <v>590</v>
       </c>
-      <c r="G3" s="102"/>
-      <c r="H3" s="103"/>
+      <c r="G3" s="103"/>
+      <c r="H3" s="104"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
@@ -17256,8 +17263,8 @@
       <c r="F4" s="7" t="s">
         <v>586</v>
       </c>
-      <c r="G4" s="104"/>
-      <c r="H4" s="105"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="106"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
@@ -17323,8 +17330,8 @@
       <c r="F5" s="5" t="s">
         <v>582</v>
       </c>
-      <c r="G5" s="104"/>
-      <c r="H5" s="105"/>
+      <c r="G5" s="105"/>
+      <c r="H5" s="106"/>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
@@ -17390,8 +17397,8 @@
       <c r="F6" s="7" t="s">
         <v>578</v>
       </c>
-      <c r="G6" s="104"/>
-      <c r="H6" s="105"/>
+      <c r="G6" s="105"/>
+      <c r="H6" s="106"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -17455,8 +17462,8 @@
       <c r="F7" s="5" t="s">
         <v>574</v>
       </c>
-      <c r="G7" s="104"/>
-      <c r="H7" s="105"/>
+      <c r="G7" s="105"/>
+      <c r="H7" s="106"/>
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -17522,8 +17529,8 @@
       <c r="F8" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="G8" s="104"/>
-      <c r="H8" s="105"/>
+      <c r="G8" s="105"/>
+      <c r="H8" s="106"/>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -17589,8 +17596,8 @@
       <c r="F9" s="5" t="s">
         <v>566</v>
       </c>
-      <c r="G9" s="104"/>
-      <c r="H9" s="105"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="106"/>
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
@@ -17656,8 +17663,8 @@
       <c r="F10" s="7" t="s">
         <v>562</v>
       </c>
-      <c r="G10" s="104"/>
-      <c r="H10" s="105"/>
+      <c r="G10" s="105"/>
+      <c r="H10" s="106"/>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
@@ -17723,8 +17730,8 @@
       <c r="F11" s="5" t="s">
         <v>558</v>
       </c>
-      <c r="G11" s="104"/>
-      <c r="H11" s="105"/>
+      <c r="G11" s="105"/>
+      <c r="H11" s="106"/>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
@@ -17790,8 +17797,8 @@
       <c r="F12" s="7" t="s">
         <v>554</v>
       </c>
-      <c r="G12" s="104"/>
-      <c r="H12" s="105"/>
+      <c r="G12" s="105"/>
+      <c r="H12" s="106"/>
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
@@ -17857,8 +17864,8 @@
       <c r="F13" s="5" t="s">
         <v>550</v>
       </c>
-      <c r="G13" s="104"/>
-      <c r="H13" s="105"/>
+      <c r="G13" s="105"/>
+      <c r="H13" s="106"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
@@ -17922,8 +17929,8 @@
       <c r="F14" s="7" t="s">
         <v>546</v>
       </c>
-      <c r="G14" s="104"/>
-      <c r="H14" s="105"/>
+      <c r="G14" s="105"/>
+      <c r="H14" s="106"/>
       <c r="I14" s="7"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -17989,8 +17996,8 @@
       <c r="F15" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="G15" s="104"/>
-      <c r="H15" s="105"/>
+      <c r="G15" s="105"/>
+      <c r="H15" s="106"/>
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
@@ -18054,8 +18061,8 @@
       <c r="F16" s="7" t="s">
         <v>538</v>
       </c>
-      <c r="G16" s="104"/>
-      <c r="H16" s="105"/>
+      <c r="G16" s="105"/>
+      <c r="H16" s="106"/>
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
@@ -18121,8 +18128,8 @@
       <c r="F17" s="5" t="s">
         <v>534</v>
       </c>
-      <c r="G17" s="104"/>
-      <c r="H17" s="105"/>
+      <c r="G17" s="105"/>
+      <c r="H17" s="106"/>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
@@ -18188,8 +18195,8 @@
       <c r="F18" s="7" t="s">
         <v>530</v>
       </c>
-      <c r="G18" s="104"/>
-      <c r="H18" s="105"/>
+      <c r="G18" s="105"/>
+      <c r="H18" s="106"/>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
@@ -18255,8 +18262,8 @@
       <c r="F19" s="5" t="s">
         <v>526</v>
       </c>
-      <c r="G19" s="104"/>
-      <c r="H19" s="105"/>
+      <c r="G19" s="105"/>
+      <c r="H19" s="106"/>
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
@@ -18322,8 +18329,8 @@
       <c r="F20" s="7" t="s">
         <v>522</v>
       </c>
-      <c r="G20" s="104"/>
-      <c r="H20" s="105"/>
+      <c r="G20" s="105"/>
+      <c r="H20" s="106"/>
       <c r="I20" s="7"/>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -18389,8 +18396,8 @@
       <c r="F21" s="5" t="s">
         <v>518</v>
       </c>
-      <c r="G21" s="104"/>
-      <c r="H21" s="105"/>
+      <c r="G21" s="105"/>
+      <c r="H21" s="106"/>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
@@ -18454,8 +18461,8 @@
       <c r="F22" s="7" t="s">
         <v>514</v>
       </c>
-      <c r="G22" s="104"/>
-      <c r="H22" s="105"/>
+      <c r="G22" s="105"/>
+      <c r="H22" s="106"/>
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -18519,8 +18526,8 @@
       <c r="F23" s="5" t="s">
         <v>510</v>
       </c>
-      <c r="G23" s="104"/>
-      <c r="H23" s="105"/>
+      <c r="G23" s="105"/>
+      <c r="H23" s="106"/>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
@@ -18586,8 +18593,8 @@
       <c r="F24" s="7" t="s">
         <v>506</v>
       </c>
-      <c r="G24" s="104"/>
-      <c r="H24" s="105"/>
+      <c r="G24" s="105"/>
+      <c r="H24" s="106"/>
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
@@ -18653,8 +18660,8 @@
       <c r="F25" s="5" t="s">
         <v>502</v>
       </c>
-      <c r="G25" s="104"/>
-      <c r="H25" s="105"/>
+      <c r="G25" s="105"/>
+      <c r="H25" s="106"/>
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
@@ -18720,8 +18727,8 @@
       <c r="F26" s="7" t="s">
         <v>498</v>
       </c>
-      <c r="G26" s="104"/>
-      <c r="H26" s="105"/>
+      <c r="G26" s="105"/>
+      <c r="H26" s="106"/>
       <c r="I26" s="7"/>
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
@@ -18785,8 +18792,8 @@
       <c r="F27" s="5" t="s">
         <v>494</v>
       </c>
-      <c r="G27" s="104"/>
-      <c r="H27" s="105"/>
+      <c r="G27" s="105"/>
+      <c r="H27" s="106"/>
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
@@ -18852,8 +18859,8 @@
       <c r="F28" s="7" t="s">
         <v>490</v>
       </c>
-      <c r="G28" s="104"/>
-      <c r="H28" s="105"/>
+      <c r="G28" s="105"/>
+      <c r="H28" s="106"/>
       <c r="I28" s="7"/>
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
@@ -18919,8 +18926,8 @@
       <c r="F29" s="5" t="s">
         <v>486</v>
       </c>
-      <c r="G29" s="104"/>
-      <c r="H29" s="105"/>
+      <c r="G29" s="105"/>
+      <c r="H29" s="106"/>
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
@@ -18986,8 +18993,8 @@
       <c r="F30" s="7" t="s">
         <v>482</v>
       </c>
-      <c r="G30" s="104"/>
-      <c r="H30" s="105"/>
+      <c r="G30" s="105"/>
+      <c r="H30" s="106"/>
       <c r="I30" s="7"/>
       <c r="J30" s="7"/>
       <c r="K30" s="7"/>
@@ -19051,8 +19058,8 @@
       <c r="F31" s="5" t="s">
         <v>478</v>
       </c>
-      <c r="G31" s="104"/>
-      <c r="H31" s="105"/>
+      <c r="G31" s="105"/>
+      <c r="H31" s="106"/>
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
@@ -19118,8 +19125,8 @@
       <c r="F32" s="7" t="s">
         <v>474</v>
       </c>
-      <c r="G32" s="104"/>
-      <c r="H32" s="105"/>
+      <c r="G32" s="105"/>
+      <c r="H32" s="106"/>
       <c r="I32" s="7"/>
       <c r="J32" s="7"/>
       <c r="K32" s="7"/>
@@ -19185,8 +19192,8 @@
       <c r="F33" s="5" t="s">
         <v>470</v>
       </c>
-      <c r="G33" s="104"/>
-      <c r="H33" s="105"/>
+      <c r="G33" s="105"/>
+      <c r="H33" s="106"/>
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
@@ -19252,8 +19259,8 @@
       <c r="F34" s="7" t="s">
         <v>466</v>
       </c>
-      <c r="G34" s="104"/>
-      <c r="H34" s="105"/>
+      <c r="G34" s="105"/>
+      <c r="H34" s="106"/>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
       <c r="K34" s="7"/>
@@ -19319,8 +19326,8 @@
       <c r="F35" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="G35" s="104"/>
-      <c r="H35" s="105"/>
+      <c r="G35" s="105"/>
+      <c r="H35" s="106"/>
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
@@ -19386,8 +19393,8 @@
       <c r="F36" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="G36" s="104"/>
-      <c r="H36" s="105"/>
+      <c r="G36" s="105"/>
+      <c r="H36" s="106"/>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>
       <c r="K36" s="7"/>
@@ -19453,8 +19460,8 @@
       <c r="F37" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="G37" s="104"/>
-      <c r="H37" s="105"/>
+      <c r="G37" s="105"/>
+      <c r="H37" s="106"/>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
@@ -19520,8 +19527,8 @@
       <c r="F38" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="G38" s="104"/>
-      <c r="H38" s="105"/>
+      <c r="G38" s="105"/>
+      <c r="H38" s="106"/>
       <c r="I38" s="7"/>
       <c r="J38" s="7"/>
       <c r="K38" s="7"/>
@@ -19587,8 +19594,8 @@
       <c r="F39" s="5" t="s">
         <v>446</v>
       </c>
-      <c r="G39" s="104"/>
-      <c r="H39" s="105"/>
+      <c r="G39" s="105"/>
+      <c r="H39" s="106"/>
       <c r="I39" s="5"/>
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
@@ -19652,8 +19659,8 @@
       <c r="F40" s="7" t="s">
         <v>442</v>
       </c>
-      <c r="G40" s="106"/>
-      <c r="H40" s="107"/>
+      <c r="G40" s="107"/>
+      <c r="H40" s="108"/>
       <c r="I40" s="7"/>
       <c r="J40" s="7"/>
       <c r="K40" s="7"/>
@@ -19802,11 +19809,11 @@
       <c r="C1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="95" t="s">
+      <c r="K1" s="96" t="s">
         <v>752</v>
       </c>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
+      <c r="L1" s="97"/>
+      <c r="M1" s="97"/>
       <c r="N1" s="36"/>
       <c r="O1" s="36"/>
       <c r="P1" s="29"/>
@@ -19831,7 +19838,7 @@
       <c r="BD1" s="25"/>
       <c r="BE1" s="25"/>
       <c r="BF1" s="9"/>
-      <c r="BG1" s="90" t="s">
+      <c r="BG1" s="91" t="s">
         <v>770</v>
       </c>
       <c r="BK1" s="25"/>
@@ -19864,107 +19871,107 @@
       <c r="F2" s="1"/>
       <c r="G2" s="9"/>
       <c r="H2" s="52"/>
-      <c r="I2" s="88" t="s">
+      <c r="I2" s="89" t="s">
         <v>759</v>
       </c>
       <c r="J2" s="36"/>
-      <c r="K2" s="97" t="s">
+      <c r="K2" s="98" t="s">
         <v>760</v>
       </c>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="100" t="s">
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="P2" s="100"/>
+      <c r="Q2" s="101" t="s">
         <v>761</v>
       </c>
-      <c r="R2" s="98"/>
-      <c r="S2" s="98"/>
-      <c r="T2" s="98"/>
-      <c r="U2" s="98"/>
-      <c r="V2" s="101"/>
-      <c r="W2" s="97" t="s">
+      <c r="R2" s="99"/>
+      <c r="S2" s="99"/>
+      <c r="T2" s="99"/>
+      <c r="U2" s="99"/>
+      <c r="V2" s="102"/>
+      <c r="W2" s="98" t="s">
         <v>762</v>
       </c>
-      <c r="X2" s="98"/>
-      <c r="Y2" s="98"/>
-      <c r="Z2" s="98"/>
-      <c r="AA2" s="98"/>
-      <c r="AB2" s="98"/>
-      <c r="AC2" s="100" t="s">
+      <c r="X2" s="99"/>
+      <c r="Y2" s="99"/>
+      <c r="Z2" s="99"/>
+      <c r="AA2" s="99"/>
+      <c r="AB2" s="99"/>
+      <c r="AC2" s="101" t="s">
         <v>763</v>
       </c>
-      <c r="AD2" s="98"/>
-      <c r="AE2" s="98"/>
-      <c r="AF2" s="98"/>
-      <c r="AG2" s="98"/>
-      <c r="AH2" s="101"/>
-      <c r="AI2" s="87" t="s">
+      <c r="AD2" s="99"/>
+      <c r="AE2" s="99"/>
+      <c r="AF2" s="99"/>
+      <c r="AG2" s="99"/>
+      <c r="AH2" s="102"/>
+      <c r="AI2" s="88" t="s">
         <v>766</v>
       </c>
-      <c r="AJ2" s="87"/>
-      <c r="AK2" s="87"/>
-      <c r="AL2" s="87"/>
-      <c r="AM2" s="87"/>
-      <c r="AN2" s="87"/>
-      <c r="AO2" s="86" t="s">
+      <c r="AJ2" s="88"/>
+      <c r="AK2" s="88"/>
+      <c r="AL2" s="88"/>
+      <c r="AM2" s="88"/>
+      <c r="AN2" s="88"/>
+      <c r="AO2" s="87" t="s">
         <v>767</v>
       </c>
-      <c r="AP2" s="87"/>
-      <c r="AQ2" s="87"/>
-      <c r="AR2" s="87"/>
-      <c r="AS2" s="87"/>
-      <c r="AT2" s="87"/>
-      <c r="AU2" s="86" t="s">
+      <c r="AP2" s="88"/>
+      <c r="AQ2" s="88"/>
+      <c r="AR2" s="88"/>
+      <c r="AS2" s="88"/>
+      <c r="AT2" s="88"/>
+      <c r="AU2" s="87" t="s">
         <v>768</v>
       </c>
-      <c r="AV2" s="87"/>
-      <c r="AW2" s="87"/>
-      <c r="AX2" s="87"/>
-      <c r="AY2" s="87"/>
-      <c r="AZ2" s="87"/>
-      <c r="BA2" s="86" t="s">
+      <c r="AV2" s="88"/>
+      <c r="AW2" s="88"/>
+      <c r="AX2" s="88"/>
+      <c r="AY2" s="88"/>
+      <c r="AZ2" s="88"/>
+      <c r="BA2" s="87" t="s">
         <v>769</v>
       </c>
-      <c r="BB2" s="87"/>
-      <c r="BC2" s="87"/>
-      <c r="BD2" s="87"/>
-      <c r="BE2" s="87"/>
-      <c r="BF2" s="87"/>
-      <c r="BG2" s="90"/>
-      <c r="BH2" s="86" t="s">
+      <c r="BB2" s="88"/>
+      <c r="BC2" s="88"/>
+      <c r="BD2" s="88"/>
+      <c r="BE2" s="88"/>
+      <c r="BF2" s="88"/>
+      <c r="BG2" s="91"/>
+      <c r="BH2" s="87" t="s">
         <v>757</v>
       </c>
-      <c r="BI2" s="87"/>
-      <c r="BJ2" s="87"/>
-      <c r="BK2" s="87"/>
-      <c r="BL2" s="87"/>
-      <c r="BM2" s="87"/>
-      <c r="BN2" s="86" t="s">
+      <c r="BI2" s="88"/>
+      <c r="BJ2" s="88"/>
+      <c r="BK2" s="88"/>
+      <c r="BL2" s="88"/>
+      <c r="BM2" s="88"/>
+      <c r="BN2" s="87" t="s">
         <v>757</v>
       </c>
-      <c r="BO2" s="87"/>
-      <c r="BP2" s="87"/>
-      <c r="BQ2" s="87"/>
-      <c r="BR2" s="87"/>
-      <c r="BS2" s="87"/>
-      <c r="BT2" s="86" t="s">
+      <c r="BO2" s="88"/>
+      <c r="BP2" s="88"/>
+      <c r="BQ2" s="88"/>
+      <c r="BR2" s="88"/>
+      <c r="BS2" s="88"/>
+      <c r="BT2" s="87" t="s">
         <v>757</v>
       </c>
-      <c r="BU2" s="87"/>
-      <c r="BV2" s="87"/>
-      <c r="BW2" s="87"/>
-      <c r="BX2" s="87"/>
-      <c r="BY2" s="87"/>
-      <c r="BZ2" s="86" t="s">
+      <c r="BU2" s="88"/>
+      <c r="BV2" s="88"/>
+      <c r="BW2" s="88"/>
+      <c r="BX2" s="88"/>
+      <c r="BY2" s="88"/>
+      <c r="BZ2" s="87" t="s">
         <v>757</v>
       </c>
-      <c r="CA2" s="87"/>
-      <c r="CB2" s="87"/>
-      <c r="CC2" s="87"/>
-      <c r="CD2" s="87"/>
-      <c r="CE2" s="87"/>
+      <c r="CA2" s="88"/>
+      <c r="CB2" s="88"/>
+      <c r="CC2" s="88"/>
+      <c r="CD2" s="88"/>
+      <c r="CE2" s="88"/>
       <c r="CF2" s="1"/>
       <c r="CG2" s="1"/>
       <c r="CH2" s="1"/>
@@ -20011,7 +20018,7 @@
       <c r="H3" s="24" t="s">
         <v>771</v>
       </c>
-      <c r="I3" s="89"/>
+      <c r="I3" s="90"/>
       <c r="J3" s="56" t="s">
         <v>773</v>
       </c>
@@ -20159,7 +20166,7 @@
       <c r="BF3" s="9" t="s">
         <v>756</v>
       </c>
-      <c r="BG3" s="91"/>
+      <c r="BG3" s="92"/>
       <c r="BH3" s="18" t="s">
         <v>753</v>
       </c>
@@ -20367,7 +20374,7 @@
         <f>AVERAGE(BA4:BE4)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="BG4" s="92"/>
+      <c r="BG4" s="93"/>
       <c r="BH4" s="66"/>
       <c r="BI4" s="61"/>
       <c r="BJ4" s="61"/>
@@ -20619,7 +20626,7 @@
         <f t="shared" ref="BF5:BF34" si="10">AVERAGE(BA5:BE5)</f>
         <v>0.45</v>
       </c>
-      <c r="BG5" s="93"/>
+      <c r="BG5" s="94"/>
       <c r="BH5" s="45"/>
       <c r="BI5" s="7"/>
       <c r="BJ5" s="7"/>
@@ -20871,7 +20878,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG6" s="93"/>
+      <c r="BG6" s="94"/>
       <c r="BH6" s="44"/>
       <c r="BI6" s="5"/>
       <c r="BJ6" s="5"/>
@@ -21125,7 +21132,7 @@
         <f t="shared" si="10"/>
         <v>0.2</v>
       </c>
-      <c r="BG7" s="93"/>
+      <c r="BG7" s="94"/>
       <c r="BH7" s="45"/>
       <c r="BI7" s="7"/>
       <c r="BJ7" s="7"/>
@@ -21377,7 +21384,7 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="BG8" s="93"/>
+      <c r="BG8" s="94"/>
       <c r="BH8" s="44"/>
       <c r="BI8" s="5"/>
       <c r="BJ8" s="5"/>
@@ -21629,7 +21636,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG9" s="93"/>
+      <c r="BG9" s="94"/>
       <c r="BH9" s="45"/>
       <c r="BI9" s="7"/>
       <c r="BJ9" s="7"/>
@@ -21881,7 +21888,7 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="BG10" s="93"/>
+      <c r="BG10" s="94"/>
       <c r="BH10" s="44"/>
       <c r="BI10" s="5"/>
       <c r="BJ10" s="5"/>
@@ -22133,7 +22140,7 @@
         <f t="shared" si="10"/>
         <v>0.1</v>
       </c>
-      <c r="BG11" s="93"/>
+      <c r="BG11" s="94"/>
       <c r="BH11" s="45"/>
       <c r="BI11" s="7"/>
       <c r="BJ11" s="7"/>
@@ -22385,7 +22392,7 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="BG12" s="93"/>
+      <c r="BG12" s="94"/>
       <c r="BH12" s="44"/>
       <c r="BI12" s="5"/>
       <c r="BJ12" s="5"/>
@@ -22637,7 +22644,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG13" s="93"/>
+      <c r="BG13" s="94"/>
       <c r="BH13" s="45"/>
       <c r="BI13" s="7"/>
       <c r="BJ13" s="7"/>
@@ -22889,7 +22896,7 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="BG14" s="93"/>
+      <c r="BG14" s="94"/>
       <c r="BH14" s="44"/>
       <c r="BI14" s="5"/>
       <c r="BJ14" s="5"/>
@@ -23141,7 +23148,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG15" s="93"/>
+      <c r="BG15" s="94"/>
       <c r="BH15" s="45"/>
       <c r="BI15" s="7"/>
       <c r="BJ15" s="7"/>
@@ -23393,7 +23400,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG16" s="93"/>
+      <c r="BG16" s="94"/>
       <c r="BH16" s="44"/>
       <c r="BI16" s="5"/>
       <c r="BJ16" s="5"/>
@@ -23645,7 +23652,7 @@
         <f t="shared" si="10"/>
         <v>0.2</v>
       </c>
-      <c r="BG17" s="93"/>
+      <c r="BG17" s="94"/>
       <c r="BH17" s="45"/>
       <c r="BI17" s="7"/>
       <c r="BJ17" s="7"/>
@@ -23895,7 +23902,7 @@
         <f t="shared" si="10"/>
         <v>0.8</v>
       </c>
-      <c r="BG18" s="93"/>
+      <c r="BG18" s="94"/>
       <c r="BH18" s="44"/>
       <c r="BI18" s="5"/>
       <c r="BJ18" s="5"/>
@@ -24067,7 +24074,7 @@
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BG19" s="93"/>
+      <c r="BG19" s="94"/>
       <c r="BH19" s="66"/>
       <c r="BI19" s="61"/>
       <c r="BJ19" s="61"/>
@@ -24319,7 +24326,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG20" s="93"/>
+      <c r="BG20" s="94"/>
       <c r="BH20" s="44"/>
       <c r="BI20" s="5"/>
       <c r="BJ20" s="5"/>
@@ -24573,7 +24580,7 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="BG21" s="93"/>
+      <c r="BG21" s="94"/>
       <c r="BH21" s="45"/>
       <c r="BI21" s="7"/>
       <c r="BJ21" s="7"/>
@@ -24825,7 +24832,7 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="BG22" s="93"/>
+      <c r="BG22" s="94"/>
       <c r="BH22" s="44"/>
       <c r="BI22" s="5"/>
       <c r="BJ22" s="5"/>
@@ -25079,7 +25086,7 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="BG23" s="93"/>
+      <c r="BG23" s="94"/>
       <c r="BH23" s="45"/>
       <c r="BI23" s="7"/>
       <c r="BJ23" s="7"/>
@@ -25333,7 +25340,7 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="BG24" s="93"/>
+      <c r="BG24" s="94"/>
       <c r="BH24" s="44"/>
       <c r="BI24" s="5"/>
       <c r="BJ24" s="5"/>
@@ -25585,7 +25592,7 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="BG25" s="93"/>
+      <c r="BG25" s="94"/>
       <c r="BH25" s="45"/>
       <c r="BI25" s="7"/>
       <c r="BJ25" s="7"/>
@@ -25841,7 +25848,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG26" s="93"/>
+      <c r="BG26" s="94"/>
       <c r="BH26" s="44"/>
       <c r="BI26" s="5"/>
       <c r="BJ26" s="5"/>
@@ -26091,7 +26098,7 @@
         <f t="shared" si="10"/>
         <v>0.8</v>
       </c>
-      <c r="BG27" s="93"/>
+      <c r="BG27" s="94"/>
       <c r="BH27" s="45"/>
       <c r="BI27" s="7"/>
       <c r="BJ27" s="7"/>
@@ -26263,7 +26270,7 @@
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BG28" s="93"/>
+      <c r="BG28" s="94"/>
       <c r="BH28" s="44"/>
       <c r="BI28" s="5"/>
       <c r="BJ28" s="5"/>
@@ -26515,7 +26522,7 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="BG29" s="93"/>
+      <c r="BG29" s="94"/>
       <c r="BH29" s="45"/>
       <c r="BI29" s="7"/>
       <c r="BJ29" s="7"/>
@@ -26767,7 +26774,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG30" s="93"/>
+      <c r="BG30" s="94"/>
       <c r="BH30" s="44"/>
       <c r="BI30" s="5"/>
       <c r="BJ30" s="5"/>
@@ -27019,7 +27026,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BG31" s="93"/>
+      <c r="BG31" s="94"/>
       <c r="BH31" s="45"/>
       <c r="BI31" s="7"/>
       <c r="BJ31" s="7"/>
@@ -27277,7 +27284,7 @@
         <f t="shared" si="10"/>
         <v>0.74</v>
       </c>
-      <c r="BG32" s="93"/>
+      <c r="BG32" s="94"/>
       <c r="BH32" s="44"/>
       <c r="BI32" s="5"/>
       <c r="BJ32" s="5"/>
@@ -27529,7 +27536,7 @@
         <f t="shared" si="10"/>
         <v>0.1</v>
       </c>
-      <c r="BG33" s="93"/>
+      <c r="BG33" s="94"/>
       <c r="BH33" s="45"/>
       <c r="BI33" s="7"/>
       <c r="BJ33" s="7"/>
@@ -27781,7 +27788,7 @@
         <f t="shared" si="10"/>
         <v>0.1</v>
       </c>
-      <c r="BG34" s="93"/>
+      <c r="BG34" s="94"/>
       <c r="BH34" s="44"/>
       <c r="BI34" s="5"/>
       <c r="BJ34" s="5"/>
@@ -28028,6 +28035,11 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="BH2:BM2"/>
+    <mergeCell ref="BN2:BS2"/>
+    <mergeCell ref="BT2:BY2"/>
+    <mergeCell ref="BZ2:CE2"/>
+    <mergeCell ref="BG4:BG34"/>
     <mergeCell ref="K1:M1"/>
     <mergeCell ref="BG1:BG3"/>
     <mergeCell ref="I2:I3"/>
@@ -28039,11 +28051,6 @@
     <mergeCell ref="AO2:AT2"/>
     <mergeCell ref="AU2:AZ2"/>
     <mergeCell ref="BA2:BF2"/>
-    <mergeCell ref="BH2:BM2"/>
-    <mergeCell ref="BN2:BS2"/>
-    <mergeCell ref="BT2:BY2"/>
-    <mergeCell ref="BZ2:CE2"/>
-    <mergeCell ref="BG4:BG34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -40284,53 +40291,53 @@
       <c r="O1" s="60" t="s">
         <v>752</v>
       </c>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="110"/>
-      <c r="V1" s="111"/>
-      <c r="W1" s="111"/>
-      <c r="X1" s="111"/>
-      <c r="Y1" s="111"/>
-      <c r="Z1" s="112"/>
-      <c r="AA1" s="110"/>
-      <c r="AB1" s="111"/>
-      <c r="AC1" s="111"/>
-      <c r="AD1" s="111"/>
-      <c r="AE1" s="111"/>
-      <c r="AF1" s="112"/>
-      <c r="AG1" s="110"/>
-      <c r="AH1" s="111"/>
-      <c r="AI1" s="111"/>
-      <c r="AJ1" s="111"/>
-      <c r="AK1" s="111"/>
-      <c r="AL1" s="112"/>
-      <c r="AM1" s="110"/>
-      <c r="AN1" s="111"/>
-      <c r="AO1" s="111"/>
-      <c r="AP1" s="111"/>
-      <c r="AQ1" s="111"/>
-      <c r="AR1" s="112"/>
-      <c r="AS1" s="110"/>
-      <c r="AT1" s="111"/>
-      <c r="AU1" s="111"/>
-      <c r="AV1" s="111"/>
-      <c r="AW1" s="111"/>
-      <c r="AX1" s="112"/>
-      <c r="AY1" s="110"/>
-      <c r="AZ1" s="111"/>
-      <c r="BA1" s="111"/>
-      <c r="BB1" s="111"/>
-      <c r="BC1" s="111"/>
-      <c r="BD1" s="112"/>
-      <c r="BE1" s="110"/>
-      <c r="BF1" s="111"/>
-      <c r="BG1" s="111"/>
-      <c r="BH1" s="111"/>
-      <c r="BI1" s="111"/>
-      <c r="BJ1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="109"/>
+      <c r="V1" s="110"/>
+      <c r="W1" s="110"/>
+      <c r="X1" s="110"/>
+      <c r="Y1" s="110"/>
+      <c r="Z1" s="111"/>
+      <c r="AA1" s="109"/>
+      <c r="AB1" s="110"/>
+      <c r="AC1" s="110"/>
+      <c r="AD1" s="110"/>
+      <c r="AE1" s="110"/>
+      <c r="AF1" s="111"/>
+      <c r="AG1" s="109"/>
+      <c r="AH1" s="110"/>
+      <c r="AI1" s="110"/>
+      <c r="AJ1" s="110"/>
+      <c r="AK1" s="110"/>
+      <c r="AL1" s="111"/>
+      <c r="AM1" s="109"/>
+      <c r="AN1" s="110"/>
+      <c r="AO1" s="110"/>
+      <c r="AP1" s="110"/>
+      <c r="AQ1" s="110"/>
+      <c r="AR1" s="111"/>
+      <c r="AS1" s="109"/>
+      <c r="AT1" s="110"/>
+      <c r="AU1" s="110"/>
+      <c r="AV1" s="110"/>
+      <c r="AW1" s="110"/>
+      <c r="AX1" s="111"/>
+      <c r="AY1" s="109"/>
+      <c r="AZ1" s="110"/>
+      <c r="BA1" s="110"/>
+      <c r="BB1" s="110"/>
+      <c r="BC1" s="110"/>
+      <c r="BD1" s="111"/>
+      <c r="BE1" s="109"/>
+      <c r="BF1" s="110"/>
+      <c r="BG1" s="110"/>
+      <c r="BH1" s="110"/>
+      <c r="BI1" s="110"/>
+      <c r="BJ1" s="111"/>
       <c r="BK1" s="49" t="s">
         <v>770</v>
       </c>
@@ -40360,70 +40367,70 @@
         <v>759</v>
       </c>
       <c r="N2" s="36"/>
-      <c r="O2" s="97" t="s">
+      <c r="O2" s="98" t="s">
         <v>760</v>
       </c>
-      <c r="P2" s="98"/>
-      <c r="Q2" s="98"/>
-      <c r="R2" s="98"/>
-      <c r="S2" s="98"/>
-      <c r="T2" s="99"/>
-      <c r="U2" s="100" t="s">
+      <c r="P2" s="99"/>
+      <c r="Q2" s="99"/>
+      <c r="R2" s="99"/>
+      <c r="S2" s="99"/>
+      <c r="T2" s="100"/>
+      <c r="U2" s="101" t="s">
         <v>761</v>
       </c>
-      <c r="V2" s="98"/>
-      <c r="W2" s="98"/>
-      <c r="X2" s="98"/>
-      <c r="Y2" s="98"/>
-      <c r="Z2" s="101"/>
-      <c r="AA2" s="97" t="s">
+      <c r="V2" s="99"/>
+      <c r="W2" s="99"/>
+      <c r="X2" s="99"/>
+      <c r="Y2" s="99"/>
+      <c r="Z2" s="102"/>
+      <c r="AA2" s="98" t="s">
         <v>762</v>
       </c>
-      <c r="AB2" s="98"/>
-      <c r="AC2" s="98"/>
-      <c r="AD2" s="98"/>
-      <c r="AE2" s="98"/>
-      <c r="AF2" s="99"/>
-      <c r="AG2" s="100" t="s">
+      <c r="AB2" s="99"/>
+      <c r="AC2" s="99"/>
+      <c r="AD2" s="99"/>
+      <c r="AE2" s="99"/>
+      <c r="AF2" s="100"/>
+      <c r="AG2" s="101" t="s">
         <v>763</v>
       </c>
-      <c r="AH2" s="98"/>
-      <c r="AI2" s="98"/>
-      <c r="AJ2" s="98"/>
-      <c r="AK2" s="98"/>
-      <c r="AL2" s="101"/>
-      <c r="AM2" s="97" t="s">
+      <c r="AH2" s="99"/>
+      <c r="AI2" s="99"/>
+      <c r="AJ2" s="99"/>
+      <c r="AK2" s="99"/>
+      <c r="AL2" s="102"/>
+      <c r="AM2" s="98" t="s">
         <v>766</v>
       </c>
-      <c r="AN2" s="98"/>
-      <c r="AO2" s="98"/>
-      <c r="AP2" s="98"/>
-      <c r="AQ2" s="98"/>
-      <c r="AR2" s="99"/>
-      <c r="AS2" s="100" t="s">
+      <c r="AN2" s="99"/>
+      <c r="AO2" s="99"/>
+      <c r="AP2" s="99"/>
+      <c r="AQ2" s="99"/>
+      <c r="AR2" s="100"/>
+      <c r="AS2" s="101" t="s">
         <v>767</v>
       </c>
-      <c r="AT2" s="98"/>
-      <c r="AU2" s="98"/>
-      <c r="AV2" s="98"/>
-      <c r="AW2" s="98"/>
-      <c r="AX2" s="99"/>
-      <c r="AY2" s="100" t="s">
+      <c r="AT2" s="99"/>
+      <c r="AU2" s="99"/>
+      <c r="AV2" s="99"/>
+      <c r="AW2" s="99"/>
+      <c r="AX2" s="100"/>
+      <c r="AY2" s="101" t="s">
         <v>768</v>
       </c>
-      <c r="AZ2" s="98"/>
-      <c r="BA2" s="98"/>
-      <c r="BB2" s="98"/>
-      <c r="BC2" s="98"/>
-      <c r="BD2" s="99"/>
-      <c r="BE2" s="100" t="s">
+      <c r="AZ2" s="99"/>
+      <c r="BA2" s="99"/>
+      <c r="BB2" s="99"/>
+      <c r="BC2" s="99"/>
+      <c r="BD2" s="100"/>
+      <c r="BE2" s="101" t="s">
         <v>769</v>
       </c>
-      <c r="BF2" s="98"/>
-      <c r="BG2" s="98"/>
-      <c r="BH2" s="98"/>
-      <c r="BI2" s="98"/>
-      <c r="BJ2" s="98"/>
+      <c r="BF2" s="99"/>
+      <c r="BG2" s="99"/>
+      <c r="BH2" s="99"/>
+      <c r="BI2" s="99"/>
+      <c r="BJ2" s="99"/>
       <c r="BK2" s="49"/>
       <c r="BL2" s="26" t="s">
         <v>757</v>
@@ -40796,8 +40803,8 @@
       <c r="D4" s="61" t="s">
         <v>161</v>
       </c>
-      <c r="E4" s="102"/>
-      <c r="F4" s="103"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="104"/>
       <c r="G4" s="61"/>
       <c r="H4" s="61"/>
       <c r="I4" s="61"/>
@@ -40968,8 +40975,8 @@
       <c r="D5" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E5" s="104"/>
-      <c r="F5" s="105"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="106"/>
       <c r="G5" s="7">
         <v>1</v>
       </c>
@@ -41241,8 +41248,8 @@
       <c r="D6" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="E6" s="104"/>
-      <c r="F6" s="105"/>
+      <c r="E6" s="105"/>
+      <c r="F6" s="106"/>
       <c r="G6" s="5">
         <v>1</v>
       </c>
@@ -41501,8 +41508,8 @@
       <c r="D7" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E7" s="104"/>
-      <c r="F7" s="105"/>
+      <c r="E7" s="105"/>
+      <c r="F7" s="106"/>
       <c r="G7" s="7">
         <v>1</v>
       </c>
@@ -41761,8 +41768,8 @@
       <c r="D8" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="E8" s="104"/>
-      <c r="F8" s="105"/>
+      <c r="E8" s="105"/>
+      <c r="F8" s="106"/>
       <c r="G8" s="5">
         <v>1</v>
       </c>
@@ -42022,8 +42029,8 @@
       <c r="D9" s="73" t="s">
         <v>161</v>
       </c>
-      <c r="E9" s="104"/>
-      <c r="F9" s="105"/>
+      <c r="E9" s="105"/>
+      <c r="F9" s="106"/>
       <c r="G9" s="73">
         <v>1</v>
       </c>
@@ -42282,8 +42289,8 @@
       <c r="D10" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="E10" s="104"/>
-      <c r="F10" s="105"/>
+      <c r="E10" s="105"/>
+      <c r="F10" s="106"/>
       <c r="G10" s="5">
         <v>1</v>
       </c>
@@ -42542,8 +42549,8 @@
       <c r="D11" s="61" t="s">
         <v>161</v>
       </c>
-      <c r="E11" s="104"/>
-      <c r="F11" s="105"/>
+      <c r="E11" s="105"/>
+      <c r="F11" s="106"/>
       <c r="G11" s="61"/>
       <c r="H11" s="61"/>
       <c r="I11" s="61"/>
@@ -42714,8 +42721,8 @@
       <c r="D12" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="E12" s="104"/>
-      <c r="F12" s="105"/>
+      <c r="E12" s="105"/>
+      <c r="F12" s="106"/>
       <c r="G12" s="5">
         <v>1</v>
       </c>
@@ -42976,8 +42983,8 @@
       <c r="D13" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E13" s="104"/>
-      <c r="F13" s="105"/>
+      <c r="E13" s="105"/>
+      <c r="F13" s="106"/>
       <c r="G13" s="7">
         <v>1</v>
       </c>
@@ -43238,8 +43245,8 @@
       <c r="D14" s="73" t="s">
         <v>161</v>
       </c>
-      <c r="E14" s="104"/>
-      <c r="F14" s="105"/>
+      <c r="E14" s="105"/>
+      <c r="F14" s="106"/>
       <c r="G14" s="73">
         <v>1</v>
       </c>
@@ -43498,8 +43505,8 @@
       <c r="D15" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E15" s="104"/>
-      <c r="F15" s="105"/>
+      <c r="E15" s="105"/>
+      <c r="F15" s="106"/>
       <c r="G15" s="7">
         <v>1</v>
       </c>
@@ -43758,8 +43765,8 @@
       <c r="D16" s="61" t="s">
         <v>161</v>
       </c>
-      <c r="E16" s="104"/>
-      <c r="F16" s="105"/>
+      <c r="E16" s="105"/>
+      <c r="F16" s="106"/>
       <c r="G16" s="61"/>
       <c r="H16" s="61"/>
       <c r="I16" s="61"/>
@@ -43930,8 +43937,8 @@
       <c r="D17" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E17" s="104"/>
-      <c r="F17" s="105"/>
+      <c r="E17" s="105"/>
+      <c r="F17" s="106"/>
       <c r="G17" s="7">
         <v>1</v>
       </c>
@@ -44192,8 +44199,8 @@
       <c r="D18" s="61" t="s">
         <v>161</v>
       </c>
-      <c r="E18" s="104"/>
-      <c r="F18" s="105"/>
+      <c r="E18" s="105"/>
+      <c r="F18" s="106"/>
       <c r="G18" s="61"/>
       <c r="H18" s="61"/>
       <c r="I18" s="61"/>
@@ -44364,8 +44371,8 @@
       <c r="D19" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E19" s="104"/>
-      <c r="F19" s="105"/>
+      <c r="E19" s="105"/>
+      <c r="F19" s="106"/>
       <c r="G19" s="7">
         <v>1</v>
       </c>
@@ -44626,8 +44633,8 @@
       <c r="D20" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="E20" s="104"/>
-      <c r="F20" s="105"/>
+      <c r="E20" s="105"/>
+      <c r="F20" s="106"/>
       <c r="G20" s="5">
         <v>1</v>
       </c>
@@ -44886,8 +44893,8 @@
       <c r="D21" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E21" s="104"/>
-      <c r="F21" s="105"/>
+      <c r="E21" s="105"/>
+      <c r="F21" s="106"/>
       <c r="G21" s="7">
         <v>1</v>
       </c>
@@ -45146,8 +45153,8 @@
       <c r="D22" s="61" t="s">
         <v>161</v>
       </c>
-      <c r="E22" s="104"/>
-      <c r="F22" s="105"/>
+      <c r="E22" s="105"/>
+      <c r="F22" s="106"/>
       <c r="G22" s="61"/>
       <c r="H22" s="61"/>
       <c r="I22" s="61"/>
@@ -45318,8 +45325,8 @@
       <c r="D23" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E23" s="104"/>
-      <c r="F23" s="105"/>
+      <c r="E23" s="105"/>
+      <c r="F23" s="106"/>
       <c r="G23" s="7">
         <v>1</v>
       </c>
@@ -45580,8 +45587,8 @@
       <c r="D24" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="E24" s="104"/>
-      <c r="F24" s="105"/>
+      <c r="E24" s="105"/>
+      <c r="F24" s="106"/>
       <c r="G24" s="5">
         <v>1</v>
       </c>
@@ -45840,8 +45847,8 @@
       <c r="D25" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E25" s="104"/>
-      <c r="F25" s="105"/>
+      <c r="E25" s="105"/>
+      <c r="F25" s="106"/>
       <c r="G25" s="7">
         <v>1</v>
       </c>
@@ -46102,8 +46109,8 @@
       <c r="D26" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="E26" s="106"/>
-      <c r="F26" s="107"/>
+      <c r="E26" s="107"/>
+      <c r="F26" s="108"/>
       <c r="G26" s="5">
         <v>1</v>
       </c>
@@ -46351,6 +46358,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="E4:F26"/>
+    <mergeCell ref="O2:T2"/>
+    <mergeCell ref="U2:Z2"/>
+    <mergeCell ref="P1:T1"/>
+    <mergeCell ref="U1:Z1"/>
+    <mergeCell ref="AA1:AF1"/>
+    <mergeCell ref="AA2:AF2"/>
+    <mergeCell ref="AG1:AL1"/>
+    <mergeCell ref="AM1:AR1"/>
+    <mergeCell ref="AS1:AX1"/>
     <mergeCell ref="AY1:BD1"/>
     <mergeCell ref="BE1:BJ1"/>
     <mergeCell ref="AG2:AL2"/>
@@ -46358,16 +46375,6 @@
     <mergeCell ref="AS2:AX2"/>
     <mergeCell ref="AY2:BD2"/>
     <mergeCell ref="BE2:BJ2"/>
-    <mergeCell ref="AA1:AF1"/>
-    <mergeCell ref="AA2:AF2"/>
-    <mergeCell ref="AG1:AL1"/>
-    <mergeCell ref="AM1:AR1"/>
-    <mergeCell ref="AS1:AX1"/>
-    <mergeCell ref="E4:F26"/>
-    <mergeCell ref="O2:T2"/>
-    <mergeCell ref="U2:Z2"/>
-    <mergeCell ref="P1:T1"/>
-    <mergeCell ref="U1:Z1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
